--- a/data/numeric/input/data_144/2.xlsx
+++ b/data/numeric/input/data_144/2.xlsx
@@ -9579,13 +9579,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A9B6073F-2A41-4DED-887F-BD4825076AA5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FEEB8647-49E7-42A5-92D6-8D6D52BD59C2}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{45DBCB2D-B5D4-4B05-808B-5605E1828AEC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4167B6E8-DF8B-4B2A-B0E9-A1523A860474}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{32B630FB-AD0B-44EE-AA08-E3EE9A89C56E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{033D1DFE-7D14-4266-B0D8-D877C9651C9D}"/>
 </file>